--- a/InputData/elec/BSpUESttGbGB/BAU Subsidy per Unit Electricity Supplied to the Grid by Grid Batteries.xlsx
+++ b/InputData/elec/BSpUESttGbGB/BAU Subsidy per Unit Electricity Supplied to the Grid by Grid Batteries.xlsx
@@ -5,52 +5,61 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\IA\elec\BSpUESttGbGB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\BSpUESttGbGB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B00C4A-FF9B-42E4-B6DD-5AAA2D0D3214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30AEC0E-7EC0-4484-AADF-96C517C42A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BSpUESttGbGB" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This file assumes developers will opt for the battery ITC, given the </t>
+  </si>
+  <si>
+    <t>incentives in the Inflation Reduction Act. Therefore, the</t>
+  </si>
+  <si>
+    <t>value for a PTC style subsidy is 0.</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Subsidy</t>
+  </si>
+  <si>
+    <t>(2012 USD / MWh)</t>
+  </si>
   <si>
     <t>BSpUESttGbGB BAU Subsidy per Unit Electricity Supplied to the Grid by Grid Batteries</t>
-  </si>
-  <si>
-    <t>Iowa</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This file assumes developers will opt for the battery ITC, given the </t>
-  </si>
-  <si>
-    <t>incentives in the Inflation Reduction Act. Therefore, the</t>
-  </si>
-  <si>
-    <t>value for a PTC style subsidy is 0.</t>
-  </si>
-  <si>
-    <t>(2012 USD / MWh)</t>
-  </si>
-  <si>
-    <t>Subsidy</t>
   </si>
 </sst>
 </file>
@@ -124,8 +133,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -135,12 +144,12 @@
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Currency 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Currency 2" xfId="5" xr:uid="{81BD210F-5FF0-4880-8028-0DC76957F95F}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{A0D66D47-893E-4339-ABA2-2AA2E8FD27AB}"/>
+    <cellStyle name="Normal 3 2" xfId="3" xr:uid="{6280AA9E-3B50-418D-82DE-98EB684B0878}"/>
+    <cellStyle name="Percent 2" xfId="4" xr:uid="{2FFD538B-3558-46F7-AC70-5718F1F53027}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -447,48 +456,45 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
@@ -500,7 +506,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -595,7 +601,7 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>0</v>
